--- a/Action/Data/CSV/Platform/PlatformId.xlsx
+++ b/Action/Data/CSV/Platform/PlatformId.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2409404\Desktop\GameProject\Action-敵追加中-\Data\CSV\Platform\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ita20\OneDrive\デスクトップ\GameProject\Action\Data\CSV\Platform\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DA57F04B-1713-4A3A-BD0B-A794FF44D30A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{82FFD05A-E3F8-4131-A6E2-2611128AE55C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A378E325-DACB-423B-896D-A4D927572F7E}"/>
+    <workbookView xWindow="3510" yWindow="3510" windowWidth="21600" windowHeight="11295" xr2:uid="{A378E325-DACB-423B-896D-A4D927572F7E}"/>
   </bookViews>
   <sheets>
     <sheet name="PlatformId" sheetId="1" r:id="rId1"/>
@@ -28,9 +28,6 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -99,9 +96,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 テーマ">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -139,7 +136,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -245,7 +242,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -387,7 +384,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -730,7 +727,7 @@
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A67">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.4">
